--- a/WorkBot/refactor-experimental/data/order_archive/Regional Distributors, Inc/Regional Distributors, Inc._Syracuse_20251223.xlsx
+++ b/WorkBot/refactor-experimental/data/order_archive/Regional Distributors, Inc/Regional Distributors, Inc._Syracuse_20251223.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,6 +483,27 @@
       </c>
       <c r="E3" t="n">
         <v>84.95</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>39808</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Wrap - Hot Sandwich Cushion (14" x 16")</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>38.64</v>
+      </c>
+      <c r="E4" t="n">
+        <v>77.28</v>
       </c>
     </row>
   </sheetData>
